--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/o-higgins.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/o-higgins.xlsx
@@ -684,7 +684,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1009,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1074,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1139,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1204,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1269,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1395,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1460,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1525,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1651,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1716,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1842,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1968,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2033,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2159,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2224,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2289,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2354,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2419,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2484,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2549,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2614,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2679,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2744,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2809,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2874,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2939,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3004,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3130,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3195,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3260,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3325,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3451,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3516,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3642,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3707,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3772,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3837,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3902,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3967,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4032,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4097,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4162,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4227,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4292,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4357,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4422,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4487,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4552,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4617,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4682,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4747,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4812,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4877,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5003,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5068,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5133,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5259,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5324,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5389,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5454,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5519,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5584,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5649,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5714,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5779,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5905,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6092,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6157,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6222,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6287,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6352,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6417,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6482,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6547,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6673,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6738,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6803,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6929,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7116,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7181,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7246,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7311,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7376,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7441,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7506,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7571,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7636,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7823,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8193,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8319,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8384,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8571,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8636,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8701,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8766,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8831,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8896,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9083,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9148,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9213,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9278,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9343,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9408,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9473,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9538,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9725,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9790,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9855,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9920,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +9985,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10050,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10115,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10180,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10245,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10310,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10436,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10562,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10810,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10875,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10940,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +11005,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11070,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11196,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11261,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11326,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11391,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11517,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11582,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11647,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11712,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11777,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11842,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11907,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11972,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +12037,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12102,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12228,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12476,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12602,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12728,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +12854,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12919,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +13045,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13110,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13175,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13240,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13305,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13431,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13496,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13561,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13626,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13691,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13817,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +14004,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14069,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14134,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14199,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14264,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14329,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14394,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14459,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14524,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14589,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14654,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14719,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14784,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14910,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +14975,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +15040,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +15105,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15170,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15357,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15422,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15487,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15613,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15678,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15743,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +15869,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +15995,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +16060,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +16125,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16251,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16316,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16381,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16446,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16511,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16576,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16641,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16706,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +16771,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +16836,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16962,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +17027,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +17092,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17218,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17283,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17348,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17413,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17478,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17543,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17608,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17673,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17738,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +17803,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +17868,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +17933,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +17998,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +18063,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +18128,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +18193,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +18258,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18323,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18449,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18514,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18579,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18705,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +18770,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +18835,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18900,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +18965,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +19030,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +19095,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +19221,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19286,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19412,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19477,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19542,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19607,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19672,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19737,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/o-higgins.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M301"/>
+  <dimension ref="A1:M313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1026,7 +1026,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3793-14-CM25</t>
+          <t>3994-44-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.090.400-4</t>
+          <t>69.081.400-5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NANCAGUA</t>
+          <t>I MUNICIPALIDAD DE OLIVAR</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1085,13 +1085,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>8168.03</v>
+        <v>8615.48</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3994-44-CM25</t>
+          <t>3793-14-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.081.400-5</t>
+          <t>69.090.400-4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLIVAR</t>
+          <t>I MUNICIPALIDAD DE NANCAGUA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>8615.48</v>
+        <v>8168.03</v>
       </c>
     </row>
     <row r="12">
@@ -1412,7 +1412,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3946-71-CM25</t>
+          <t>3946-70-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1471,13 +1471,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2733.1</v>
+        <v>4811.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3946-70-CM25</t>
+          <t>3946-71-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1517,12 +1517,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>4811.5</v>
+        <v>2733.1</v>
       </c>
     </row>
     <row r="18">
@@ -1668,7 +1668,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2777-54-CM25</t>
+          <t>2817-115-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.090.100-5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1708,32 +1708,28 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2974</v>
+        <v>17072.93</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2817-115-CM25</t>
+          <t>2777-54-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1758,12 +1754,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.090.100-5</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1773,22 +1769,26 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>17072.93</v>
+        <v>2974</v>
       </c>
     </row>
     <row r="22">
@@ -2176,7 +2176,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3038-36-CM25</t>
+          <t>4371-65-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.090.500-0</t>
+          <t>69.081.000-k</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOLOL</t>
+          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2235,13 +2235,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>11200.88</v>
+        <v>14249.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4371-65-CM25</t>
+          <t>3038-36-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.081.000-k</t>
+          <t>69.090.500-0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+          <t>I MUNICIPALIDAD DE LOLOL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>14249.7</v>
+        <v>11200.88</v>
       </c>
     </row>
     <row r="30">
@@ -2761,7 +2761,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1256505-71-CM25</t>
+          <t>3863-42-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2781,17 +2781,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>71.015.300-0</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICENTE</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2801,32 +2801,28 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMERCIAL FELP SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>76.427.199-8</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>11650.1</v>
+        <v>28131.6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3690-70-CM25</t>
+          <t>3500-45-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2846,17 +2842,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.080.800-5</t>
+          <t>69.081.700-4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
+          <t>I MUNICIPALIDAD DE QUINTA DE TILCOCO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2866,12 +2862,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2885,13 +2881,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2760.62</v>
+        <v>6535.48</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3635-72-CM25</t>
+          <t>3690-69-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2916,12 +2912,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.081.500-1</t>
+          <t>69.080.800-5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MALLOA</t>
+          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2931,12 +2927,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2950,13 +2946,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>6461.96</v>
+        <v>4099.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3690-69-CM25</t>
+          <t>3635-72-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2981,12 +2977,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.080.800-5</t>
+          <t>69.081.500-1</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
+          <t>I MUNICIPALIDAD DE MALLOA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2996,12 +2992,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3015,13 +3011,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>4099.5</v>
+        <v>6461.96</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3863-42-CM25</t>
+          <t>3690-70-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3041,17 +3037,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>69.080.800-5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3061,28 +3057,32 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>COMERCIAL FELP SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.427.199-8</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>28131.6</v>
+        <v>2760.62</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3500-45-CM25</t>
+          <t>1256505-71-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3102,17 +3102,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.081.700-4</t>
+          <t>71.015.300-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTA DE TILCOCO</t>
+          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3122,17 +3122,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>6535.48</v>
+        <v>11650.1</v>
       </c>
     </row>
     <row r="43">
@@ -3342,7 +3342,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4732-67-CM25</t>
+          <t>3864-44-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3362,17 +3362,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3382,28 +3382,32 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>21313.8</v>
+        <v>9111.84</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3864-44-CM25</t>
+          <t>4732-67-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3423,17 +3427,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3443,26 +3447,22 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.292.976-7</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>9111.84</v>
+        <v>21313.8</v>
       </c>
     </row>
     <row r="48">
@@ -4179,7 +4179,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>557639-682-CM25</t>
+          <t>3863-163-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4199,17 +4199,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>71.014.200-9</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>6901.76</v>
+        <v>36717.45</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3863-163-CM25</t>
+          <t>557639-682-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4264,17 +4264,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>71.014.200-9</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>36717.45</v>
+        <v>6901.76</v>
       </c>
     </row>
     <row r="61">
@@ -4439,7 +4439,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2778-480-CM25</t>
+          <t>2778-481-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4498,13 +4498,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3114.17</v>
+        <v>2984.47</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2778-481-CM25</t>
+          <t>557639-772-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>71.014.200-9</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4563,13 +4563,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2984.47</v>
+        <v>32224.25</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>557639-772-CM25</t>
+          <t>2778-480-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>71.014.200-9</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>32224.25</v>
+        <v>3114.17</v>
       </c>
     </row>
     <row r="66">
@@ -4894,7 +4894,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4563-51-CM25</t>
+          <t>4563-52-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4934,28 +4934,32 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2700.59</v>
+        <v>3416.25</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4563-52-CM25</t>
+          <t>4563-51-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4995,26 +4999,22 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.292.976-7</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>3416.25</v>
+        <v>2700.59</v>
       </c>
     </row>
     <row r="72">
@@ -5150,7 +5150,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3635-177-CM25</t>
+          <t>2817-457-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.081.500-1</t>
+          <t>69.090.100-5</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MALLOA</t>
+          <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5190,28 +5190,32 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.596.570-5</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>7925.26</v>
+        <v>16919.42</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2817-457-CM25</t>
+          <t>3635-177-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5236,12 +5240,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.090.100-5</t>
+          <t>69.081.500-1</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
+          <t>I MUNICIPALIDAD DE MALLOA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5251,26 +5255,22 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.596.570-5</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>16919.42</v>
+        <v>7925.26</v>
       </c>
     </row>
     <row r="76">
@@ -5406,7 +5406,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2678-117-CM25</t>
+          <t>2678-116-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5465,13 +5465,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>21886.48</v>
+        <v>9644.07</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2678-116-CM25</t>
+          <t>2678-117-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>9644.07</v>
+        <v>21886.48</v>
       </c>
     </row>
     <row r="80">
@@ -6239,7 +6239,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4371-120-CM25</t>
+          <t>4371-119-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6298,13 +6298,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>7045.63</v>
+        <v>3015.22</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4371-119-CM25</t>
+          <t>4371-120-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6344,12 +6344,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6363,7 +6363,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3015.22</v>
+        <v>7045.63</v>
       </c>
     </row>
     <row r="93">
@@ -7068,7 +7068,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>4738-334-CM25</t>
+          <t>3683-98-CM25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>69.080.800-5</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7108,12 +7108,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -7127,13 +7127,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>9396.51</v>
+        <v>8285.32</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>3683-98-CM25</t>
+          <t>4738-334-CM25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>69.080.800-5</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>8285.32</v>
+        <v>9396.51</v>
       </c>
     </row>
     <row r="106">
@@ -7962,7 +7962,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2566-323-CM25</t>
+          <t>3635-287-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7987,12 +7987,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>69.090.700-3</t>
+          <t>69.081.500-1</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHEPICA</t>
+          <t>I MUNICIPALIDAD DE MALLOA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -8017,7 +8017,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>39133.84</v>
+        <v>6510.63</v>
       </c>
     </row>
     <row r="119">
@@ -8084,7 +8084,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3635-287-CM25</t>
+          <t>2566-323-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>69.081.500-1</t>
+          <t>69.090.700-3</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MALLOA</t>
+          <t>I MUNICIPALIDAD DE CHEPICA</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -8139,7 +8139,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>6510.63</v>
+        <v>39133.84</v>
       </c>
     </row>
     <row r="121">
@@ -8271,7 +8271,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>3992-218-CM25</t>
+          <t>3958-237-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8296,12 +8296,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>69.080.700-9</t>
+          <t>69.073.800-7</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLTAUCO</t>
+          <t>I MUNICIPALIDAD DE NAVIDAD</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8311,26 +8311,22 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.292.976-7</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>5131.03</v>
+        <v>6997.2</v>
       </c>
     </row>
     <row r="124">
@@ -8401,7 +8397,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>3958-237-CM25</t>
+          <t>3992-218-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8426,12 +8422,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>69.073.800-7</t>
+          <t>69.080.700-9</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NAVIDAD</t>
+          <t>I MUNICIPALIDAD DE COLTAUCO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8441,22 +8437,26 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>6997.2</v>
+        <v>5131.03</v>
       </c>
     </row>
     <row r="126">
@@ -9035,7 +9035,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>3928-1139-CM25</t>
+          <t>3928-1132-CM25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9075,12 +9075,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -9094,13 +9094,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>4243.54</v>
+        <v>3646.06</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>3928-1132-CM25</t>
+          <t>3928-1139-CM25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9140,12 +9140,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -9159,13 +9159,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>3646.06</v>
+        <v>4243.54</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>557639-2320-CM25</t>
+          <t>3863-415-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9185,17 +9185,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>71.014.200-9</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -9224,13 +9224,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>37332.68</v>
+        <v>2558.5</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>3863-415-CM25</t>
+          <t>557639-2320-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9250,17 +9250,17 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>71.014.200-9</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9270,12 +9270,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -9289,7 +9289,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2558.5</v>
+        <v>37332.68</v>
       </c>
     </row>
     <row r="139">
@@ -10453,7 +10453,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3997-26-CM26</t>
+          <t>923000-3-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10478,12 +10478,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>69.080.700-9</t>
+          <t>69.081.400-5</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLTAUCO</t>
+          <t>I MUNICIPALIDAD DE OLIVAR</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10493,28 +10493,32 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr"/>
+          <t>78.218.816-K</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>11223.94</v>
+        <v>5464.4</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>923000-3-CM26</t>
+          <t>3997-26-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10539,12 +10543,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>69.081.400-5</t>
+          <t>69.080.700-9</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLIVAR</t>
+          <t>I MUNICIPALIDAD DE COLTAUCO</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10554,26 +10558,22 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.179.170-2</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>5464.4</v>
+        <v>11223.94</v>
       </c>
     </row>
     <row r="159">
@@ -10892,7 +10892,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2776-48-CM26</t>
+          <t>1183926-15-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10917,12 +10917,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>65.199.122-6</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL DE LA REGIÓN DEL LIBERTADOR GENERA</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10932,17 +10932,17 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -10951,13 +10951,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>10429.26</v>
+        <v>40414.78</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1183926-15-CM26</t>
+          <t>2776-48-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>65.199.122-6</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL DE LA REGIÓN DEL LIBERTADOR GENERA</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10997,17 +10997,17 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -11016,13 +11016,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>40414.78</v>
+        <v>10429.26</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2401-70-CM26</t>
+          <t>1375760-9-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11042,17 +11042,17 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>69.080.100-0</t>
+          <t>61.981.310-3</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RANCAGUA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE CACHAPOAL</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -11062,12 +11062,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -11081,13 +11081,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>30849.19</v>
+        <v>1612.45</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1375760-7-CM26</t>
+          <t>2401-70-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11107,17 +11107,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.981.310-3</t>
+          <t>69.080.100-0</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE CACHAPOAL</t>
+          <t>I MUNICIPALIDAD DE RANCAGUA</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -11127,28 +11127,32 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>38212.33</v>
+        <v>30849.19</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1375760-9-CM26</t>
+          <t>1375760-7-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11188,26 +11192,22 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1612.45</v>
+        <v>38212.33</v>
       </c>
     </row>
     <row r="169">
@@ -11343,7 +11343,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1375760-12-CM26</t>
+          <t>1126920-28-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11368,12 +11368,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>61.981.310-3</t>
+          <t>62.000.790-0</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE CACHAPOAL</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE COLCHAGUA</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11383,32 +11383,28 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>6294.01</v>
+        <v>12565.64</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1126920-28-CM26</t>
+          <t>1375760-12-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11433,12 +11429,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>62.000.790-0</t>
+          <t>61.981.310-3</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE COLCHAGUA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE CACHAPOAL</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11448,22 +11444,26 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>12565.64</v>
+        <v>6294.01</v>
       </c>
     </row>
     <row r="173">
@@ -11859,7 +11859,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2675-65-CM26</t>
+          <t>557639-241-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11879,17 +11879,17 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>71.014.200-9</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11899,12 +11899,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -11918,13 +11918,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>5316.92</v>
+        <v>20506.08</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>557639-241-CM26</t>
+          <t>2675-65-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11944,17 +11944,17 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>71.014.200-9</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11964,12 +11964,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -11983,7 +11983,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>20506.08</v>
+        <v>5316.92</v>
       </c>
     </row>
     <row r="181">
@@ -12245,7 +12245,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2402-44-CM26</t>
+          <t>3928-149-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12265,17 +12265,17 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>69.080.100-0</t>
+          <t>69.091.201-5</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RANCAGUA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -12285,12 +12285,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -12300,13 +12300,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>7218.43</v>
+        <v>10245.9</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>3928-149-CM26</t>
+          <t>2402-44-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12326,17 +12326,17 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>69.091.201-5</t>
+          <t>69.080.100-0</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>I MUNICIPALIDAD DE RANCAGUA</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
@@ -12361,7 +12361,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>10245.9</v>
+        <v>7218.43</v>
       </c>
     </row>
     <row r="187">
@@ -12680,7 +12680,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>3500-46-CM26</t>
+          <t>3928-187-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12700,17 +12700,17 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>69.081.700-4</t>
+          <t>69.091.201-5</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTA DE TILCOCO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12720,32 +12720,28 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>6870.47</v>
+        <v>9553.200000000001</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>3928-187-CM26</t>
+          <t>3500-46-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12765,17 +12761,17 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>69.091.201-5</t>
+          <t>69.081.700-4</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>I MUNICIPALIDAD DE QUINTA DE TILCOCO</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12785,22 +12781,26 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr"/>
+          <t>77.727.285-3</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>9553.200000000001</v>
+        <v>6870.47</v>
       </c>
     </row>
     <row r="194">
@@ -13062,7 +13062,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>3014-114-CM26</t>
+          <t>4737-39-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -13082,17 +13082,17 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>69.081.600-8</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COINCO</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -13102,12 +13102,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -13121,13 +13121,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>6168.82</v>
+        <v>11731.08</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>4737-39-CM26</t>
+          <t>3014-114-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13147,17 +13147,17 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>69.081.600-8</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>I MUNICIPALIDAD DE COINCO</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -13167,12 +13167,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>11731.08</v>
+        <v>6168.82</v>
       </c>
     </row>
     <row r="200">
@@ -13448,7 +13448,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>3928-309-CM26</t>
+          <t>3928-311-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13488,12 +13488,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -13507,13 +13507,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>2308.59</v>
+        <v>1025.78</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>3928-311-CM26</t>
+          <t>3928-309-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13553,12 +13553,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -13572,7 +13572,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1025.78</v>
+        <v>2308.59</v>
       </c>
     </row>
     <row r="206">
@@ -14086,7 +14086,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>4161-178-CM26</t>
+          <t>4164-245-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -14126,12 +14126,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -14145,7 +14145,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>25446.96</v>
+        <v>26494.12</v>
       </c>
     </row>
     <row r="215">
@@ -14216,7 +14216,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>4164-245-CM26</t>
+          <t>4161-178-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -14256,12 +14256,12 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -14275,7 +14275,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>26494.12</v>
+        <v>25446.96</v>
       </c>
     </row>
     <row r="217">
@@ -14476,7 +14476,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>3863-166-CM26</t>
+          <t>3500-114-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14496,17 +14496,17 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>69.081.700-4</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>I MUNICIPALIDAD DE QUINTA DE TILCOCO</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14516,12 +14516,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -14535,13 +14535,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>16905.56</v>
+        <v>1736.81</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>3500-114-CM26</t>
+          <t>3863-166-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14561,17 +14561,17 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>69.081.700-4</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTA DE TILCOCO</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14581,12 +14581,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -14600,7 +14600,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>1736.81</v>
+        <v>16905.56</v>
       </c>
     </row>
     <row r="222">
@@ -14671,7 +14671,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>3810-298-CM26</t>
+          <t>3478-159-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14696,12 +14696,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>69.081.700-4</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>I MUNICIPALIDAD DE QUINTA DE TILCOCO</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14711,32 +14711,28 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr"/>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>46060.38</v>
+        <v>7614.81</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2778-298-CM26</t>
+          <t>3810-298-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14756,17 +14752,17 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14776,12 +14772,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -14795,13 +14791,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>6590.82</v>
+        <v>46060.38</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>3478-159-CM26</t>
+          <t>2778-298-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14821,17 +14817,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>69.081.700-4</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTA DE TILCOCO</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14841,28 +14837,32 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K225" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>7614.81</v>
+        <v>6590.82</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1213444-218-CM26</t>
+          <t>3959-52-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14887,12 +14887,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>71.328.600-1</t>
+          <t>69.073.800-7</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
+          <t>I MUNICIPALIDAD DE NAVIDAD</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14902,12 +14902,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -14921,13 +14921,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>8143.41</v>
+        <v>1344.34</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1213444-219-CM26</t>
+          <t>3959-51-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14952,12 +14952,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>71.328.600-1</t>
+          <t>69.073.800-7</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
+          <t>I MUNICIPALIDAD DE NAVIDAD</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14967,12 +14967,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -14986,13 +14986,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>45338.29</v>
+        <v>2674.88</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>3959-51-CM26</t>
+          <t>1213444-219-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -15017,12 +15017,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>69.073.800-7</t>
+          <t>71.328.600-1</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NAVIDAD</t>
+          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -15051,13 +15051,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>2674.88</v>
+        <v>45338.29</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>3959-52-CM26</t>
+          <t>1213444-218-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -15082,12 +15082,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>69.073.800-7</t>
+          <t>71.328.600-1</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NAVIDAD</t>
+          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -15097,12 +15097,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -15116,13 +15116,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>1344.34</v>
+        <v>8143.41</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>4737-90-CM26</t>
+          <t>3177-174-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -15142,17 +15142,17 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>69.080.200-7</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -15181,13 +15181,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>19457.71</v>
+        <v>3164.02</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>889473-833-CM26</t>
+          <t>4737-90-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -15212,12 +15212,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -15227,22 +15227,26 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
-        </is>
-      </c>
-      <c r="K231" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>4267.34</v>
+        <v>19457.71</v>
       </c>
     </row>
     <row r="232">
@@ -15309,7 +15313,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>3177-174-CM26</t>
+          <t>889473-833-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -15329,17 +15333,17 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>69.080.200-7</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -15349,26 +15353,22 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.152.668-3</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr"/>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>3164.02</v>
+        <v>4267.34</v>
       </c>
     </row>
     <row r="234">
@@ -15821,7 +15821,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>3478-195-CM26</t>
+          <t>2778-362-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15841,17 +15841,17 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>69.081.700-4</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTA DE TILCOCO</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15861,17 +15861,17 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -15880,13 +15880,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>1412.22</v>
+        <v>814.14</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>3478-196-CM26</t>
+          <t>3478-195-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15926,28 +15926,32 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
-        </is>
-      </c>
-      <c r="K242" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>882.98</v>
+        <v>1412.22</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2778-362-CM26</t>
+          <t>3478-196-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15967,17 +15971,17 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.081.700-4</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>I MUNICIPALIDAD DE QUINTA DE TILCOCO</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15987,26 +15991,22 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K243" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr"/>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>814.14</v>
+        <v>882.98</v>
       </c>
     </row>
     <row r="244">
@@ -16142,7 +16142,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>4737-110-CM26</t>
+          <t>889473-1026-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -16167,12 +16167,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -16182,28 +16182,32 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K246" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>14904.75</v>
+        <v>4108.68</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>889473-1026-CM26</t>
+          <t>4737-110-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -16228,12 +16232,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -16243,26 +16247,22 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>4108.68</v>
+        <v>14904.75</v>
       </c>
     </row>
     <row r="248">
@@ -16658,7 +16658,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>3634-285-CM26</t>
+          <t>889473-1142-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16683,12 +16683,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>69.081.500-1</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MALLOA</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -16717,7 +16717,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>1628.68</v>
+        <v>3748.44</v>
       </c>
     </row>
     <row r="255">
@@ -16788,7 +16788,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>889473-1142-CM26</t>
+          <t>3634-285-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16813,12 +16813,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>69.081.500-1</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>I MUNICIPALIDAD DE MALLOA</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16828,12 +16828,12 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -16847,13 +16847,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>3748.44</v>
+        <v>1628.68</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1398-896-CM26</t>
+          <t>4563-36-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16873,17 +16873,17 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>61.606.800-8</t>
+          <t>69.080.300-3</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+          <t>I MUNICIPALIDAD DE GRANEROS</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16893,28 +16893,32 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K257" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>828.24</v>
+        <v>12109.44</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>4563-36-CM26</t>
+          <t>1398-896-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16934,17 +16938,17 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>69.080.300-3</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GRANEROS</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16954,26 +16958,22 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>12109.44</v>
+        <v>828.24</v>
       </c>
     </row>
     <row r="259">
@@ -17109,7 +17109,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>3810-609-CM26</t>
+          <t>4738-211-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -17134,12 +17134,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -17149,28 +17149,32 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K261" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>1589.82</v>
+        <v>4879.05</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>3810-610-CM26</t>
+          <t>557639-1504-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -17190,17 +17194,17 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>71.014.200-9</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -17210,12 +17214,12 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
@@ -17229,13 +17233,13 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>3505.74</v>
+        <v>3955.02</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>557639-1504-CM26</t>
+          <t>3810-610-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -17255,17 +17259,17 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>71.014.200-9</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -17275,12 +17279,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -17294,13 +17298,13 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>3955.02</v>
+        <v>3505.74</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>4738-211-CM26</t>
+          <t>3810-609-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -17325,12 +17329,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -17340,26 +17344,22 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
-        </is>
-      </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>4879.05</v>
+        <v>1589.82</v>
       </c>
     </row>
     <row r="265">
@@ -17495,7 +17495,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>557639-1584-CM26</t>
+          <t>889473-1311-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17515,17 +17515,17 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>71.014.200-9</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17535,12 +17535,12 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -17554,7 +17554,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>1701</v>
+        <v>2437.94</v>
       </c>
     </row>
     <row r="268">
@@ -17625,7 +17625,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>889473-1311-CM26</t>
+          <t>557639-1584-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17645,17 +17645,17 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>71.014.200-9</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -17665,12 +17665,12 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -17684,13 +17684,13 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>2437.94</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>4563-46-CM26</t>
+          <t>2678-118-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17715,12 +17715,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>69.080.300-3</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GRANEROS</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17730,12 +17730,12 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
@@ -17749,7 +17749,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>8559.08</v>
+        <v>11984.49</v>
       </c>
     </row>
     <row r="271">
@@ -17820,7 +17820,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2678-118-CM26</t>
+          <t>4563-46-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17845,12 +17845,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>69.080.300-3</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE GRANEROS</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17860,12 +17860,12 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -17879,7 +17879,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>11984.49</v>
+        <v>8559.08</v>
       </c>
     </row>
     <row r="273">
@@ -18275,7 +18275,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2675-354-CM26</t>
+          <t>2675-358-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -18315,12 +18315,12 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -18334,7 +18334,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>4574.96</v>
+        <v>2658.46</v>
       </c>
     </row>
     <row r="280">
@@ -18401,7 +18401,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2675-358-CM26</t>
+          <t>2675-354-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -18441,12 +18441,12 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -18460,7 +18460,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>2658.46</v>
+        <v>4574.96</v>
       </c>
     </row>
     <row r="282">
@@ -18787,7 +18787,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>557639-1950-CM26</t>
+          <t>3691-144-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -18812,12 +18812,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>71.014.200-9</t>
+          <t>69.080.800-5</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -18827,12 +18827,12 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
@@ -18846,13 +18846,13 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>20284.03</v>
+        <v>12728.84</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>3691-144-CM26</t>
+          <t>557639-1950-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -18877,12 +18877,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>69.080.800-5</t>
+          <t>71.014.200-9</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -18892,12 +18892,12 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -18911,7 +18911,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>12728.84</v>
+        <v>20284.03</v>
       </c>
     </row>
     <row r="289">
@@ -19047,7 +19047,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>557639-2124-CM26</t>
+          <t>889473-1542-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -19067,17 +19067,17 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>71.014.200-9</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -19087,17 +19087,17 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -19106,7 +19106,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>1582.01</v>
+        <v>40703.36</v>
       </c>
     </row>
     <row r="292">
@@ -19173,7 +19173,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>889473-1542-CM26</t>
+          <t>557639-2124-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -19193,17 +19193,17 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>71.014.200-9</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -19213,17 +19213,17 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -19232,13 +19232,13 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>40703.36</v>
+        <v>1582.01</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2675-402-CM26</t>
+          <t>3635-181-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -19263,12 +19263,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>69.081.500-1</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE MALLOA</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -19278,32 +19278,28 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr"/>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>3681.86</v>
+        <v>22361.19</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>3635-181-CM26</t>
+          <t>2675-402-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -19323,17 +19319,17 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>69.081.500-1</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MALLOA</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -19343,28 +19339,32 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K295" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>22361.19</v>
+        <v>3681.86</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1193180-39-CM26</t>
+          <t>2087-46-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -19384,17 +19384,17 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>60.511.060-6</t>
+          <t>60.511.141-6</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL LIBERTADOR BERNARDO  O´HIGGINS</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CARDENAL CARO</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -19404,12 +19404,12 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -19423,7 +19423,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>3152.31</v>
+        <v>3154.81</v>
       </c>
     </row>
     <row r="297">
@@ -19494,7 +19494,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2087-46-CM26</t>
+          <t>1193180-39-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19519,12 +19519,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>60.511.141-6</t>
+          <t>60.511.060-6</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CARDENAL CARO</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL LIBERTADOR BERNARDO  O´HIGGINS</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -19534,12 +19534,12 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>96.513.980-k</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>3154.81</v>
+        <v>3152.31</v>
       </c>
     </row>
     <row r="299">
@@ -19644,7 +19644,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -19709,7 +19709,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -19749,6 +19749,774 @@
       </c>
       <c r="M301" s="2" t="n">
         <v>10013.85</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>3864-309-CM26</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>69.090.600-7</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>COMPUTACION E INGENIERIA S A</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M302" s="2" t="n">
+        <v>29727.39</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>4562-525-CM26</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>69.080.300-3</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE GRANEROS</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>76.128.275-1</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M303" s="2" t="n">
+        <v>4241.73</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>3992-187-CM26</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>69.080.700-9</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COLTAUCO</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>76.128.275-1</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M304" s="2" t="n">
+        <v>35720.72</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>4374-64-CM26</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>72.240.400-9</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M305" s="2" t="n">
+        <v>30176.02</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>4374-65-CM26</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>72.240.400-9</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M306" s="2" t="n">
+        <v>7429.23</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>4374-66-CM26</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>72.240.400-9</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr"/>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M307" s="2" t="n">
+        <v>2583.25</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>889473-1831-CM26</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>61.980.530-5</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M308" s="2" t="n">
+        <v>4521.76</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>1562-469-CM26</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>61.702.000-9</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>RICOH</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M309" s="2" t="n">
+        <v>1388.37</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>4371-454-CM26</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>69.081.000-k</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>77.508.642-4</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M310" s="2" t="n">
+        <v>620.97</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>3793-247-CM26</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>69.090.400-4</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NANCAGUA</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>76.596.570-5</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr"/>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M311" s="2" t="n">
+        <v>16088.61</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>1398-1348-CM26</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>61.606.800-8</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr"/>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M312" s="2" t="n">
+        <v>153.51</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>889473-2046-CM26</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>61.980.530-5</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>76.128.275-1</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M313" s="2" t="n">
+        <v>192.66</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/o-higgins.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/o-higgins.xlsx
@@ -10282,7 +10282,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -15142,7 +15142,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -16999,7 +16999,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -18551,7 +18551,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -18742,7 +18742,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
